--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-18T23:52:42+00:00</t>
+    <t>2023-01-19T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-20T17:48:12+00:00</t>
+    <t>2023-01-25T15:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T22:08:27+00:00</t>
+    <t>2023-01-31T04:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T18:46:21+00:00</t>
+    <t>2023-02-07T12:10:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T07:55:54+00:00</t>
+    <t>2023-02-09T15:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T15:16:32+00:00</t>
+    <t>2023-02-09T17:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T17:43:27+00:00</t>
+    <t>2023-02-09T21:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T21:16:20+00:00</t>
+    <t>2023-02-10T06:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T06:44:21+00:00</t>
+    <t>2023-02-10T12:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T12:56:00+00:00</t>
+    <t>2023-02-10T14:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T14:37:40+00:00</t>
+    <t>2023-02-10T15:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T15:20:03+00:00</t>
+    <t>2023-02-10T23:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T23:42:05+00:00</t>
+    <t>2023-02-13T12:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T12:09:55+00:00</t>
+    <t>2023-02-13T14:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:15:11+00:00</t>
+    <t>2023-02-13T14:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:19:18+00:00</t>
+    <t>2023-02-13T18:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:35:48+00:00</t>
+    <t>2023-02-13T18:37:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:37:08+00:00</t>
+    <t>2023-02-13T18:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:51:39+00:00</t>
+    <t>2023-02-13T20:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T20:10:13+00:00</t>
+    <t>2023-02-14T12:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:41:39+00:00</t>
+    <t>2023-02-14T14:58:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:58:50+00:00</t>
+    <t>2023-02-14T15:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T15:00:34+00:00</t>
+    <t>2023-02-14T18:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T18:30:52+00:00</t>
+    <t>2023-02-14T21:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:17:51+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-15T16:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:22:21+00:00</t>
+    <t>2023-02-15T20:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T20:04:03+00:00</t>
+    <t>2023-02-16T23:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-16T23:28:10+00:00</t>
+    <t>2023-02-17T19:45:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-17T19:45:07+00:00</t>
+    <t>2023-02-20T03:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T15:31:02+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -366,6 +366,12 @@
     <t>Value of extension</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://minsal.cl/listaespera/ValueSet/VSPuebloIndigena</t>
+  </si>
+  <si>
     <t>Extension.extension.value[x].id</t>
   </si>
   <si>
@@ -469,12 +475,6 @@
   </si>
   <si>
     <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://minsal.cl/listaespera/ValueSet/VSPuebloIndigena</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1881,13 +1881,11 @@
         <v>72</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="X10" s="2"/>
       <c r="Y10" t="s" s="2">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="Z10" t="s" s="2">
         <v>72</v>
@@ -1925,7 +1923,7 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -2025,11 +2023,11 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
@@ -2051,13 +2049,13 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
@@ -2127,7 +2125,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -2150,19 +2148,19 @@
         <v>93</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O13" t="s" s="2">
         <v>72</v>
@@ -2211,7 +2209,7 @@
         <v>72</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>73</v>
@@ -2226,12 +2224,12 @@
         <v>110</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -2331,11 +2329,11 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -2357,13 +2355,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
@@ -2433,7 +2431,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -2459,16 +2457,16 @@
         <v>97</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>72</v>
@@ -2517,7 +2515,7 @@
         <v>72</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>73</v>
@@ -2532,12 +2530,12 @@
         <v>110</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -2563,13 +2561,13 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
@@ -2619,7 +2617,7 @@
         <v>72</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>73</v>
@@ -2634,12 +2632,12 @@
         <v>110</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -2662,17 +2660,17 @@
         <v>93</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O18" t="s" s="2">
         <v>72</v>
@@ -2697,11 +2695,13 @@
         <v>72</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="X18" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Y18" t="s" s="2">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>72</v>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PuebloIndigena.xlsx
+++ b/StructureDefinition-PuebloIndigena.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
